--- a/data/trans_orig/P62A$jubilacion-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P62A$jubilacion-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2007</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2007 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>447440</t>
+          <t>446945</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>473854</t>
+          <t>473421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>147348</t>
+          <t>145204</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188935</t>
+          <t>189351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>599322</t>
+          <t>600413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>657886</t>
+          <t>659506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>221683</t>
+          <t>220631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264990</t>
+          <t>265020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220573</t>
+          <t>219338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>273442</t>
+          <t>274510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32466</t>
+          <t>32136</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57286</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39037</t>
+          <t>39419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54965</t>
+          <t>55472</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87923</t>
+          <t>87154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12386</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29754</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129840</t>
+          <t>129658</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148119</t>
+          <t>148363</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151416</t>
+          <t>152161</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182131</t>
+          <t>182188</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24346</t>
+          <t>24356</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42006</t>
+          <t>42060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>23261</t>
+          <t>22988</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45482</t>
+          <t>45611</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>35290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54595</t>
+          <t>54427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>18790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>21126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49849</t>
+          <t>49064</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58894</t>
+          <t>58755</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24078</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35222</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76159</t>
+          <t>77372</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92489</t>
+          <t>92895</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13696</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16070</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>638560</t>
+          <t>638499</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>673151</t>
+          <t>672924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>202158</t>
+          <t>201156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>248046</t>
+          <t>247086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>846704</t>
+          <t>847160</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>915506</t>
+          <t>914828</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>259080</t>
+          <t>262575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>307049</t>
+          <t>309304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>257740</t>
+          <t>256818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>317638</t>
+          <t>314441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56950</t>
+          <t>57073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90081</t>
+          <t>90981</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>63012</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101582</t>
+          <t>100677</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>142040</t>
+          <t>140889</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>39179</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23706</t>
+          <t>23990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46446</t>
+          <t>48784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>444259</t>
+          <t>442849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>480157</t>
+          <t>479628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>174445</t>
+          <t>176354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>222086</t>
+          <t>223044</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>628346</t>
+          <t>628440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>695248</t>
+          <t>693458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>12750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257708</t>
+          <t>258050</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304503</t>
+          <t>304159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>255355</t>
+          <t>253722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>316408</t>
+          <t>312421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,77%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46922</t>
+          <t>47930</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78261</t>
+          <t>78303</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25064</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47627</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78399</t>
+          <t>78312</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117340</t>
+          <t>118693</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13722</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34279</t>
+          <t>34056</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>24252</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49378</t>
+          <t>48796</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44180</t>
+          <t>43329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79516</t>
+          <t>74436</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148580</t>
+          <t>148126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>182998</t>
+          <t>183262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32346</t>
+          <t>31824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56576</t>
+          <t>56430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>187733</t>
+          <t>189851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233687</t>
+          <t>233500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>26653</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50856</t>
+          <t>49456</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>27529</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51197</t>
+          <t>52539</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57163</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88842</t>
+          <t>89218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26080</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49179</t>
+          <t>50975</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91205</t>
+          <t>90358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129935</t>
+          <t>131075</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49183</t>
+          <t>48138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41603</t>
+          <t>41794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66367</t>
+          <t>67533</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75102</t>
+          <t>73361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108643</t>
+          <t>108092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>29447</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41463</t>
+          <t>41407</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27294</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48577</t>
+          <t>48350</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65955</t>
+          <t>65405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>11262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>22863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14493</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>636929</t>
+          <t>637236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>689792</t>
+          <t>690164</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239760</t>
+          <t>235753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292369</t>
+          <t>291374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>882591</t>
+          <t>887518</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>968882</t>
+          <t>968409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>295134</t>
+          <t>295850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349169</t>
+          <t>349342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>294397</t>
+          <t>292184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364316</t>
+          <t>359494</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>121586</t>
+          <t>119292</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>166805</t>
+          <t>166641</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63130</t>
+          <t>61657</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>97070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>191483</t>
+          <t>191108</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>252285</t>
+          <t>250319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44746</t>
+          <t>45649</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76908</t>
+          <t>77051</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78783</t>
+          <t>79448</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116333</t>
+          <t>116127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>132340</t>
+          <t>129928</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182109</t>
+          <t>178829</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2016 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>387959</t>
+          <t>386680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>411569</t>
+          <t>412218</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144163</t>
+          <t>148535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187190</t>
+          <t>187981</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>538372</t>
+          <t>539660</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>596950</t>
+          <t>599077</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173642</t>
+          <t>170990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>220302</t>
+          <t>215111</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170010</t>
+          <t>169348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>221070</t>
+          <t>220765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13319</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32507</t>
+          <t>32585</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34504</t>
+          <t>34702</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31527</t>
+          <t>30727</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59463</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27200</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35018</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62593</t>
+          <t>64328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50716</t>
+          <t>49061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84345</t>
+          <t>82214</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>270738</t>
+          <t>268391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>305492</t>
+          <t>305166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99022</t>
+          <t>100493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>131816</t>
+          <t>132463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380116</t>
+          <t>380194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>429640</t>
+          <t>431348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49280</t>
+          <t>50293</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79870</t>
+          <t>80848</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>49139</t>
+          <t>48086</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>82110</t>
+          <t>83388</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46709</t>
+          <t>47564</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76371</t>
+          <t>78856</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40378</t>
+          <t>40088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71868</t>
+          <t>71636</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107267</t>
+          <t>108394</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5638,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>26674</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49053</t>
+          <t>49848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39221</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66976</t>
+          <t>67691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71857</t>
+          <t>72509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>107522</t>
+          <t>109130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51418</t>
+          <t>52375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64832</t>
+          <t>64433</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>42580</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>84478</t>
+          <t>85276</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103253</t>
+          <t>103451</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11385</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>9527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -6094,12 +6094,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>22305</t>
+          <t>20901</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>725584</t>
+          <t>726670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>773690</t>
+          <t>771837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>286860</t>
+          <t>289356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>345881</t>
+          <t>348000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1028163</t>
+          <t>1023484</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1109884</t>
+          <t>1102623</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>235814</t>
+          <t>233960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>291293</t>
+          <t>291863</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>232831</t>
+          <t>235693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>298327</t>
+          <t>299146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69692</t>
+          <t>71148</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107352</t>
+          <t>108551</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>40155</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68287</t>
+          <t>70075</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120265</t>
+          <t>120952</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169523</t>
+          <t>169066</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44719</t>
+          <t>45300</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74952</t>
+          <t>76799</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>89137</t>
+          <t>88383</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>129602</t>
+          <t>130874</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142494</t>
+          <t>142246</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>190674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>152573</t>
+          <t>155244</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182294</t>
+          <t>183172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83544</t>
+          <t>83995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>108190</t>
+          <t>109132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>243964</t>
+          <t>243630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>284017</t>
+          <t>282633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29644</t>
+          <t>29204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>48366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>17094</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31334</t>
+          <t>30479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50395</t>
+          <t>49849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74672</t>
+          <t>74153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>187478</t>
+          <t>186639</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>213952</t>
+          <t>215230</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>189489</t>
+          <t>188561</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>222845</t>
+          <t>226738</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74310</t>
+          <t>73940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101025</t>
+          <t>100508</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49061</t>
+          <t>48447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69190</t>
+          <t>68821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129348</t>
+          <t>126920</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162904</t>
+          <t>159699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160271</t>
+          <t>162656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>196054</t>
+          <t>197109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150972</t>
+          <t>151448</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>422540</t>
+          <t>416057</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344446</t>
+          <t>345128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>673574</t>
+          <t>669399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66984</t>
+          <t>66550</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94802</t>
+          <t>96288</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60886</t>
+          <t>57767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56508</t>
+          <t>55077</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>153523</t>
+          <t>152015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>30095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143112</t>
+          <t>142007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39395</t>
+          <t>41389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113523</t>
+          <t>113951</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113698</t>
+          <t>113318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144813</t>
+          <t>146051</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25171</t>
+          <t>26849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140977</t>
+          <t>141022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98855</t>
+          <t>102341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>277422</t>
+          <t>276329</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59467</t>
+          <t>59772</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77268</t>
+          <t>77028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38517</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>51046</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103265</t>
+          <t>102352</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124726</t>
+          <t>123710</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>25701</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -8149,12 +8149,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20680</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35900</t>
+          <t>35994</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8164,82 +8164,82 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>33,22%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>15563</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>10823</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>21184</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>21,04%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>14,63%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>43277</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>34797</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>53516</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>23,74%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>19,09%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>15563</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>10590</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>21225</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>28,69%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>43277</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>34577</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>53679</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>23,74%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>18,97%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>389792</t>
+          <t>389427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>440321</t>
+          <t>439651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287804</t>
+          <t>287980</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>658728</t>
+          <t>694010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>722469</t>
+          <t>722321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1129292</t>
+          <t>1138947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,66%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112096</t>
+          <t>110799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149063</t>
+          <t>152098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32023</t>
+          <t>30141</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83126</t>
+          <t>82751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>129410</t>
+          <t>128103</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228385</t>
+          <t>227177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19340</t>
+          <t>18370</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>157386</t>
+          <t>141369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>374948</t>
+          <t>374352</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>202838</t>
+          <t>207204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>346862</t>
+          <t>347644</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>221612</t>
+          <t>218724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>264341</t>
+          <t>264824</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8620,12 +8620,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82184</t>
+          <t>75010</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>199918</t>
+          <t>199601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>278943</t>
+          <t>263369</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457869</t>
+          <t>457037</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8690,12 +8690,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P62A$jubilacion-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P62A$jubilacion-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>446945</t>
+          <t>446248</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>473421</t>
+          <t>474445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>145204</t>
+          <t>146685</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>189351</t>
+          <t>187931</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>600413</t>
+          <t>600923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>659506</t>
+          <t>660951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220631</t>
+          <t>221479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265020</t>
+          <t>264006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>219338</t>
+          <t>219773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>274510</t>
+          <t>275725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32136</t>
+          <t>32315</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>56868</t>
+          <t>57575</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39419</t>
+          <t>37838</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55472</t>
+          <t>55805</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87154</t>
+          <t>88576</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>12431</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31033</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129658</t>
+          <t>128379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148363</t>
+          <t>147518</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19153</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36950</t>
+          <t>36692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152161</t>
+          <t>150699</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182188</t>
+          <t>180700</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>41817</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22988</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45611</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>17034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35290</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24188</t>
+          <t>25296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30034</t>
+          <t>29774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54427</t>
+          <t>53788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18790</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21126</t>
+          <t>21607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49064</t>
+          <t>49127</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58755</t>
+          <t>58822</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24158</t>
+          <t>24299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>35653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77372</t>
+          <t>77533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92895</t>
+          <t>92517</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12817</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16358</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>638499</t>
+          <t>639437</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>672924</t>
+          <t>672786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>201156</t>
+          <t>202254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>247086</t>
+          <t>249874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>847160</t>
+          <t>850179</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>914828</t>
+          <t>919693</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,99%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>262575</t>
+          <t>261261</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>309304</t>
+          <t>309755</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>256818</t>
+          <t>255092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>314441</t>
+          <t>312903</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>58227</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90981</t>
+          <t>90227</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63012</t>
+          <t>60881</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100677</t>
+          <t>99271</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140889</t>
+          <t>142305</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39179</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>23649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48784</t>
+          <t>46759</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>442849</t>
+          <t>443750</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>479628</t>
+          <t>480217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176354</t>
+          <t>176945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223044</t>
+          <t>220669</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>628440</t>
+          <t>631298</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>693458</t>
+          <t>695513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258050</t>
+          <t>256635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304159</t>
+          <t>301811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>253722</t>
+          <t>253312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>312421</t>
+          <t>314780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47930</t>
+          <t>46451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78303</t>
+          <t>78087</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25501</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48147</t>
+          <t>48619</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78312</t>
+          <t>80156</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118693</t>
+          <t>121033</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48796</t>
+          <t>48625</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3197,12 +3197,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43329</t>
+          <t>43935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74436</t>
+          <t>76604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3212,12 +3212,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148126</t>
+          <t>149343</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>183262</t>
+          <t>183271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31824</t>
+          <t>32363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56430</t>
+          <t>56525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189851</t>
+          <t>189214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>233500</t>
+          <t>234802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,63%</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26653</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49456</t>
+          <t>50675</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26571</t>
+          <t>27235</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52539</t>
+          <t>52406</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>59584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89218</t>
+          <t>90289</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26533</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50975</t>
+          <t>49653</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90358</t>
+          <t>89828</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131075</t>
+          <t>130841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>25231</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48138</t>
+          <t>48700</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41794</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67533</t>
+          <t>68007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73361</t>
+          <t>73089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108092</t>
+          <t>108400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29447</t>
+          <t>28535</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41407</t>
+          <t>41321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48350</t>
+          <t>47202</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65405</t>
+          <t>65664</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,87%</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11262</t>
+          <t>12406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22863</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>637236</t>
+          <t>637542</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>690164</t>
+          <t>690588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>235753</t>
+          <t>239858</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>291374</t>
+          <t>293169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>887518</t>
+          <t>882982</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>968409</t>
+          <t>968649</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,05%</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>11358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>295850</t>
+          <t>295735</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349342</t>
+          <t>350024</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>292184</t>
+          <t>291979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>359494</t>
+          <t>358893</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119292</t>
+          <t>120614</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>166641</t>
+          <t>166691</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61657</t>
+          <t>62531</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>97070</t>
+          <t>97179</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>191108</t>
+          <t>194062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>250319</t>
+          <t>253429</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45649</t>
+          <t>45409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77051</t>
+          <t>77814</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79448</t>
+          <t>78119</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>116127</t>
+          <t>114807</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129928</t>
+          <t>132185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178829</t>
+          <t>182943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>386680</t>
+          <t>388002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>412218</t>
+          <t>411584</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>148535</t>
+          <t>145784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187981</t>
+          <t>190482</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>539660</t>
+          <t>536221</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>599077</t>
+          <t>594823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170990</t>
+          <t>171365</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215111</t>
+          <t>213473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169348</t>
+          <t>168373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>220765</t>
+          <t>220946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32585</t>
+          <t>32237</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34702</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30727</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56959</t>
+          <t>58419</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11108</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27634</t>
+          <t>27577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35185</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64328</t>
+          <t>64267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49061</t>
+          <t>50194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82214</t>
+          <t>82319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>268391</t>
+          <t>272512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>305166</t>
+          <t>306945</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>100493</t>
+          <t>99981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>132463</t>
+          <t>132223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>380194</t>
+          <t>379866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>431348</t>
+          <t>428240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50293</t>
+          <t>48149</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80848</t>
+          <t>79006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48086</t>
+          <t>49401</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83388</t>
+          <t>82077</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47564</t>
+          <t>46045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78856</t>
+          <t>77321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>18071</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40088</t>
+          <t>39573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71636</t>
+          <t>70608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108394</t>
+          <t>107870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5638,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26674</t>
+          <t>26095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49848</t>
+          <t>49004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39637</t>
+          <t>39957</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67691</t>
+          <t>65784</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72509</t>
+          <t>70893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109130</t>
+          <t>108459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>52249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64433</t>
+          <t>64419</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29258</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42580</t>
+          <t>42331</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85276</t>
+          <t>85403</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>103451</t>
+          <t>104344</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>5017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17059</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -6094,12 +6094,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14792</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20901</t>
+          <t>21145</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>726670</t>
+          <t>723647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>771837</t>
+          <t>770361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289356</t>
+          <t>293164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>348000</t>
+          <t>348988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1023484</t>
+          <t>1027050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1102623</t>
+          <t>1104839</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233960</t>
+          <t>236826</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>291863</t>
+          <t>288528</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235693</t>
+          <t>233824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299146</t>
+          <t>298760</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71148</t>
+          <t>70893</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108551</t>
+          <t>110156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40155</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>70075</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120952</t>
+          <t>121363</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169066</t>
+          <t>166381</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45300</t>
+          <t>45014</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76799</t>
+          <t>75196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88383</t>
+          <t>88794</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>130874</t>
+          <t>129417</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>142246</t>
+          <t>141609</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>190674</t>
+          <t>190709</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>180635</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155244</t>
+          <t>165961</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183172</t>
+          <t>196472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>96161</t>
+          <t>104957</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83995</t>
+          <t>91614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109132</t>
+          <t>118436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>264361</t>
+          <t>285591</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>243630</t>
+          <t>265987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>282633</t>
+          <t>307749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,05%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38170</t>
+          <t>39339</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29204</t>
+          <t>29826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48366</t>
+          <t>51162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17094</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>60912</t>
+          <t>63651</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49849</t>
+          <t>51740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74153</t>
+          <t>76790</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12785</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>200630</t>
+          <t>216991</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>186639</t>
+          <t>202202</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>215230</t>
+          <t>232887</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>206797</t>
+          <t>223500</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>188561</t>
+          <t>205287</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>226738</t>
+          <t>243670</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86331</t>
+          <t>94309</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73940</t>
+          <t>80226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100508</t>
+          <t>108884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7267,32 +7267,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58036</t>
+          <t>64808</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48447</t>
+          <t>52977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68821</t>
+          <t>77182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>144367</t>
+          <t>159118</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>126920</t>
+          <t>141374</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159699</t>
+          <t>177335</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179423</t>
+          <t>195681</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162656</t>
+          <t>176480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>197109</t>
+          <t>214027</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>295183</t>
+          <t>100479</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151448</t>
+          <t>87787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>416057</t>
+          <t>113549</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>474606</t>
+          <t>296160</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>345128</t>
+          <t>274325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>669399</t>
+          <t>319226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80322</t>
+          <t>84258</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66550</t>
+          <t>69191</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96288</t>
+          <t>100940</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>34383</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57767</t>
+          <t>43126</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>111989</t>
+          <t>118640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55077</t>
+          <t>100908</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>152015</t>
+          <t>136103</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79018</t>
+          <t>84967</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30095</t>
+          <t>72359</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>142007</t>
+          <t>97926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>83164</t>
+          <t>89255</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41389</t>
+          <t>76895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113951</t>
+          <t>105199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>128294</t>
+          <t>143540</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113318</t>
+          <t>126760</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146051</t>
+          <t>163898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7723,32 +7723,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77836</t>
+          <t>84785</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26849</t>
+          <t>71820</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141022</t>
+          <t>98739</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>206130</t>
+          <t>228325</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102341</t>
+          <t>208004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>276329</t>
+          <t>249815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68683</t>
+          <t>78461</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>59772</t>
+          <t>68582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77028</t>
+          <t>88260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44740</t>
+          <t>52183</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>45222</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51046</t>
+          <t>58617</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>113424</t>
+          <t>130644</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102352</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123710</t>
+          <t>142604</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>27925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>845</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4190</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13200</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -8144,32 +8144,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27715</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>23838</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35994</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8179,32 +8179,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>18571</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21184</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8214,32 +8214,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>43277</t>
+          <t>50456</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>39605</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53516</t>
+          <t>60817</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>416308</t>
+          <t>454776</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>389427</t>
+          <t>429254</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>439651</t>
+          <t>484663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>436084</t>
+          <t>257619</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287980</t>
+          <t>236605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>694010</t>
+          <t>276298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>852391</t>
+          <t>712395</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>722321</t>
+          <t>679146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1138947</t>
+          <t>747210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>135375</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>110799</t>
+          <t>115504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152098</t>
+          <t>155605</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>66164</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>55451</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82751</t>
+          <t>79875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>190581</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128103</t>
+          <t>181402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227177</t>
+          <t>225195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18370</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>286750</t>
+          <t>309410</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>141369</t>
+          <t>287312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>374352</t>
+          <t>331601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>297898</t>
+          <t>321051</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>207204</t>
+          <t>298475</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>347644</t>
+          <t>348021</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -8600,32 +8600,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>269735</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>218724</t>
+          <t>242942</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>264824</t>
+          <t>294537</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8635,32 +8635,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>151435</t>
+          <t>168164</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>75010</t>
+          <t>150945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>199601</t>
+          <t>186161</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8670,32 +8670,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>393774</t>
+          <t>437899</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>263369</t>
+          <t>408863</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457037</t>
+          <t>469291</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
